--- a/docs/Logic Requirements/Ageipelago Prithviraj.xlsx
+++ b/docs/Logic Requirements/Ageipelago Prithviraj.xlsx
@@ -5,15 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb6dd295c338e39f/Desktop/Logic Requirements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{D8D1E62D-C866-4C4B-AD89-FCFEA44E110C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4F490CF-7C73-4580-BB7D-3D498EE284EE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4534A02-F6D5-438C-B085-77ED9ABE570A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Prithviraj" sheetId="1" r:id="rId1"/>
+    <sheet name="Born of Fire" sheetId="2" r:id="rId2"/>
+    <sheet name="The Digvijaya" sheetId="7" r:id="rId3"/>
+    <sheet name="Hand of a Princess" sheetId="8" r:id="rId4"/>
+    <sheet name="The Fate of India" sheetId="9" r:id="rId5"/>
+    <sheet name="The Legend of Prithviraj" sheetId="10" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="214">
   <si>
     <t>Scenario</t>
   </si>
@@ -365,96 +370,6 @@
 10 Camel Riders
 10 Light Cavalry
 27 Cavalry Archers</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-4 Archers
-10 Crossbowmen
-1 Camel Scout
-5 Scouts
-4 Light Cavalry
-5 Elephant Archers
-2 Armored Elephants
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-15 Crossbowmen
-6 Shrivamsha Riders
-12 Light Cavalry
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-10 Crossbowmen
-4 Shrivamsha Riders
-8 Light Cavalry
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-20 Crossbowmen
-8 Shrivamsha Riders
-16 Light Cavalry</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1769,94 +1684,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Starting Units:
-4 Men-at-Arms
-4 Spearmen
-1 Scout
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-4 Men-at-Arms
-4 Spearmen
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-3 Men-at-Arms
-3 Spearmen
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-5 Men-at-Arms
-5 Spearmen</t>
-    </r>
-  </si>
-  <si>
-    <t>Winning with 12 Minutes or more remaining is both a side Objective and a Steam Achievement.
-Since this Mission is on a Timer, I suggest turning it due to the added Objectives.
-I have no idea why Player 6 can train Units…</t>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Reach </t>
     </r>
     <r>
@@ -2310,95 +2137,1117 @@
     </r>
   </si>
   <si>
+    <t>4 Poets</t>
+  </si>
+  <si>
+    <t>Starting Units:
+Bhima
+Subhatavarman
+Paramardi
+Vijayasimha</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Convert 1/2/3/4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rajas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Yadava</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Chola</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF2FE2F5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pagan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Defend against all </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ghorid Raids</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+2 Light Cavalry
+2 Elite Elephant Archers
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+11 Chakram Throwers
+15 Elite Shrivamsha Riders
+12 Elite Elephant Archers
+5 Siege Elephants
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+8 Chakram Throwers
+12 Elite Shrivamsha Riders
+8 Elite Elephant Archers
+4 Siege Elephants
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+14 Chakram Throwers
+18 Elite Shrivamsha Riders
+12 Elite Elephant Archers
+6 Siege Elephants</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+1 Scout
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+13 Champions
+11 Halberdiers
+11 Elite Urumi Swordsmen
+8 Elite Elephant Archers
+3 Trebuchets
+5 Galleons (If the Player builds a Dock)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+10 Champions
+8 Halberdiers
+8 Elite Urumi Swordsmen
+5 Elite Elephant Archers
+2 Trebuchets
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+16 Champions
+14 Halberdiers
+14 Elite Urumi Swordsmen
+11 Elite Elephant Archers
+4 Trebuchets
+5 Galleons (If the Player builds a Dock)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+4 Long Swordsmen
+6 Arambai
+1 War Galley
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+11 Champions
+8 Elite Battle Elephants
+8 Elite Arambai
+4 Heavy Scorpions
+5 Capped Rams
+8 Galleons
+4 Fire Ships
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+8 Champions
+5 Elite Battle Elephants
+6 Elite Arambai
+3 Heavy Scorpions
+6 Galleons
+2 Fire Ships
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+13 Champions
+10 Elite Battle Elephants
+10 Elite Arambai
+5 Heavy Scorpions
+6 Capped Rams
+10 Galleons
+6 Fire Ships</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+84 Elite Ghulams
+21 Imperial Camel Riders
+29 Heavy Camel Riders
+1 Onager
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+75 Elite Ghulams
+75 Heavy Cavalry Archers
+75 Imperial Camel Riders
+4 Siege Elephants
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+50 Elite Ghulams
+50 Heavy Cavalry Archers
+50 Imperial Camel Riders
+2 Siege Elephants
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+100 Elite Ghulams
+100 Heavy Cavalry Archers
+100 Imperial Camel Riders
+6 Siege Elephants</t>
+    </r>
+  </si>
+  <si>
+    <t>6 Villagers, 1 Town Center, Misc. Units/Buildings (Indian Dynasties) x4
+Max Population Limit +25 x3</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Indian Dynasties</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ghorids</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Collect 1/2 Relic/s
+Destroy the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF2FE2F5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Wonder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Destroy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1/2/3/4/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>5/6/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>7/8/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF2FE2F5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Castle/s
+</t>
+    </r>
+  </si>
+  <si>
+    <t>The Player needs to have unlocked Monasteries and Monks to collect Relics.</t>
+  </si>
+  <si>
+    <t>400 Food, 400 Wood, 300 Gold, 100 Stone x4
+Technology: 1 of Husbandry, Light Cavalry, Chain Barding Armor, Bow Saw
+Technology: 1 of Fervor, Sanctity, Long Swordsman, Arson, Chain Mail Armor, Heavy Plow
+Technology: 1 of Thumb Ring, Bodkin Arrow, Leather Archer Armor, Stone Shaft Mining
+Technology: 1 of Ballistics, Murder Holes, Guard Tower, Gold Shaft Mining
+Technology: Kshatriyas
+Technology: Frontier Guards
+Castles can be built</t>
+  </si>
+  <si>
+    <t>In Vanilla, the Player cannot build Castles in the Beginning.
+The Ghorids' Trade seems to be malfunctioning, it looks like the Trade Carts are repeatedly ordered back to the allied Market, so they never deliver their Gold.
+The Techs mentioned in the usefull items are given when a Raja has been converted, but only 1 of each Selection.</t>
+  </si>
+  <si>
+    <t>This Player recieves the Units Player 7 has created whenever a Raid happens.</t>
+  </si>
+  <si>
+    <t>Restrictions</t>
+  </si>
+  <si>
+    <t>Killable Units</t>
+  </si>
+  <si>
+    <t>Destructible Buildings</t>
+  </si>
+  <si>
+    <t>Castle - Imperial Age</t>
+  </si>
+  <si>
+    <t>Deer</t>
+  </si>
+  <si>
+    <t>No items required</t>
+  </si>
+  <si>
+    <t>Guard Tower</t>
+  </si>
+  <si>
+    <t>Buildings</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Technologies</t>
+  </si>
+  <si>
+    <t>Fortified Wall</t>
+  </si>
+  <si>
+    <t>Unrestricted</t>
+  </si>
+  <si>
+    <t>Fortified Gate</t>
+  </si>
+  <si>
+    <t>Goat</t>
+  </si>
+  <si>
+    <t>Sea Wall</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>Sea Gate</t>
+  </si>
+  <si>
+    <t>Dock</t>
+  </si>
+  <si>
+    <t>Long Swordsman</t>
+  </si>
+  <si>
+    <t>Scorpion</t>
+  </si>
+  <si>
+    <t>Mill</t>
+  </si>
+  <si>
+    <t>Monk</t>
+  </si>
+  <si>
+    <t>Barracks</t>
+  </si>
+  <si>
+    <t>Siege Workshop</t>
+  </si>
+  <si>
+    <t>Lumber Camp</t>
+  </si>
+  <si>
+    <t>Town Center</t>
+  </si>
+  <si>
+    <t>House</t>
+  </si>
+  <si>
+    <t>Stable</t>
+  </si>
+  <si>
+    <t>Onager</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Blacksmith</t>
+  </si>
+  <si>
+    <t>Monastery</t>
+  </si>
+  <si>
+    <t>Wonder</t>
+  </si>
+  <si>
+    <t>Castle</t>
+  </si>
+  <si>
+    <t>Mangonel</t>
+  </si>
+  <si>
+    <t>University</t>
+  </si>
+  <si>
+    <t>Archery Range</t>
+  </si>
+  <si>
+    <t>Mining Camp</t>
+  </si>
+  <si>
+    <t>Fishing Ship</t>
+  </si>
+  <si>
+    <t>Fire Ship</t>
+  </si>
+  <si>
+    <t>Elephant Archer</t>
+  </si>
+  <si>
+    <t>Crossbowman</t>
+  </si>
+  <si>
+    <t>Light Cavalry</t>
+  </si>
+  <si>
+    <t>Armored Elephant</t>
+  </si>
+  <si>
+    <t>Elephant</t>
+  </si>
+  <si>
+    <t>Tiger</t>
+  </si>
+  <si>
+    <t>Wild Camel</t>
+  </si>
+  <si>
+    <t>Camel Rider</t>
+  </si>
+  <si>
+    <t>Shrivamsha Rider</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+4 Archers
+10 Crossbowmen
+1 Camel Scout
+5 Scouts
+4 Light Cavalry
+5 Elephant Archers
+2 Armored Elephants
+1 Nagarjuna
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+15 Crossbowmen
+6 Shrivamsha Riders
+12 Light Cavalry
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+10 Crossbowmen
+4 Shrivamsha Riders
+8 Light Cavalry
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+20 Crossbowmen
+8 Shrivamsha Riders
+16 Light Cavalry</t>
+    </r>
+  </si>
+  <si>
+    <t>Trade Cart</t>
+  </si>
+  <si>
+    <t>Nagarjuna</t>
+  </si>
+  <si>
+    <t>Spearman</t>
+  </si>
+  <si>
+    <t>Camel Scout</t>
+  </si>
+  <si>
+    <t>Galley</t>
+  </si>
+  <si>
+    <t>War Galley</t>
+  </si>
+  <si>
+    <t>Requires Dock</t>
+  </si>
+  <si>
+    <t>Elite Skirmisher</t>
+  </si>
+  <si>
+    <t>Cavalry Archer</t>
+  </si>
+  <si>
+    <t>Chakram Thrower</t>
+  </si>
+  <si>
+    <t>Stone Wall</t>
+  </si>
+  <si>
+    <t>Stone Gate</t>
+  </si>
+  <si>
+    <t>Farm</t>
+  </si>
+  <si>
+    <t>Watch Tower</t>
+  </si>
+  <si>
+    <t>Fortifed Gate</t>
+  </si>
+  <si>
+    <t>Tent</t>
+  </si>
+  <si>
+    <t>Tent (Large)</t>
+  </si>
+  <si>
+    <t>Outpost</t>
+  </si>
+  <si>
+    <t>Feudal - Castle Age</t>
+  </si>
+  <si>
+    <t>Fortifed Tower</t>
+  </si>
+  <si>
+    <t>Ibex</t>
+  </si>
+  <si>
+    <t>Rhinoceros</t>
+  </si>
+  <si>
+    <t>Water Buffalo</t>
+  </si>
+  <si>
+    <t>Crocodile</t>
+  </si>
+  <si>
+    <t>Eastern Swordsman</t>
+  </si>
+  <si>
+    <t>Canoe</t>
+  </si>
+  <si>
+    <t>Scout Cavalry</t>
+  </si>
+  <si>
+    <t>Demolition Ship</t>
+  </si>
+  <si>
+    <t>Raja</t>
+  </si>
+  <si>
+    <t>Skirmisher</t>
+  </si>
+  <si>
+    <t>Sea Tower</t>
+  </si>
+  <si>
+    <t>Palisade Wall</t>
+  </si>
+  <si>
+    <t>Rice Farm</t>
+  </si>
+  <si>
+    <t>Fence</t>
+  </si>
+  <si>
+    <t>Fortified Tower</t>
+  </si>
+  <si>
+    <t>Winning with 12 Minutes or more remaining is both a side Objective and a Steam Achievement.
+Since this Mission is on a Timer, I suggest turning it off due to the added Objectives.
+I have no idea why Player 6 can train Units…</t>
+  </si>
+  <si>
+    <t>Pikeman</t>
+  </si>
+  <si>
+    <t>Man-at-Arms</t>
+  </si>
+  <si>
+    <t>Imperial Camel Rider</t>
+  </si>
+  <si>
+    <t>Transport Ship Required</t>
+  </si>
+  <si>
+    <t>Heavy Camel Rider</t>
+  </si>
+  <si>
+    <t>Not on Standard</t>
+  </si>
+  <si>
+    <t>Transport Ship Required
+Not on Standard</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+4 Men-at-Arms
+4 Spearmen
+1 Scout Cavalry
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+4 Men-at-Arms
+4 Spearmen
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+3 Men-at-Arms
+3 Spearmen
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+5 Men-at-Arms
+5 Spearmen</t>
+    </r>
+  </si>
+  <si>
+    <t>Merchant</t>
+  </si>
+  <si>
+    <t>Dock Required</t>
+  </si>
+  <si>
+    <t>Yurt</t>
+  </si>
+  <si>
+    <t>Trade Workshop</t>
+  </si>
+  <si>
+    <t>Fire Tower</t>
+  </si>
+  <si>
+    <t>Sanchi Stupa</t>
+  </si>
+  <si>
+    <t>Army Tent</t>
+  </si>
+  <si>
+    <t>Army Tent (Large)</t>
+  </si>
+  <si>
+    <t>Transport Ship</t>
+  </si>
+  <si>
+    <t>Unavailable</t>
+  </si>
+  <si>
+    <t>No Villager
+No Trade Cart
+No Monk
+No Chakram Thrower
+No Petard</t>
+  </si>
+  <si>
+    <t>Wild Bactrian Camel</t>
+  </si>
+  <si>
+    <t>Muhammad Ghori</t>
+  </si>
+  <si>
+    <t>Siege Elephant</t>
+  </si>
+  <si>
+    <t>Hussar</t>
+  </si>
+  <si>
+    <t>Heavy Cavalry Archer</t>
+  </si>
+  <si>
+    <t>Knight</t>
+  </si>
+  <si>
+    <t>War Elephant</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Starting Units:
 4 Keshiks
 6 Cavalry Archers
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-30 Savars
-15 Elite War Elephants
-3 Onagers
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-20 Savars
-10 Elite War Elephants
-2 Onagers
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-40 Savars
-20 Elite War Elephants
-4 Onagers</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-6 Knights
-5 War Elephants
 </t>
     </r>
     <r>
@@ -2486,99 +3335,119 @@
     </r>
   </si>
   <si>
-    <t>4 Poets</t>
-  </si>
-  <si>
-    <t>Starting Units:
-Bhima
-Subhatavarman
-Paramardi
-Vijayasimha</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Convert 1/2/3/4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Rajas</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Yadava</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Chola</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF2FE2F5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Pagan</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Defend against all </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ghorid Raids</t>
-    </r>
+    <r>
+      <t xml:space="preserve">Starting Units:
+6 Knights
+5 War Elephants
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+30 Savars
+15 Elite War Elephants
+3 Onagers
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+20 Savars
+10 Elite War Elephants
+2 Onagers
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+40 Savars
+20 Elite War Elephants
+4 Onagers</t>
+    </r>
+  </si>
+  <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
+    <t>Savar</t>
+  </si>
+  <si>
+    <t>Elite War Elephant</t>
+  </si>
+  <si>
+    <t>Keshik</t>
+  </si>
+  <si>
+    <t>Elite Keshik</t>
+  </si>
+  <si>
+    <t>Heavy Scorpion</t>
+  </si>
+  <si>
+    <t>Trebuchet</t>
+  </si>
+  <si>
+    <t>Monk (Hero)</t>
+  </si>
+  <si>
+    <t>Only on Hard Logic</t>
+  </si>
+  <si>
+    <t>Elite Elephant Archer</t>
   </si>
   <si>
     <r>
@@ -2614,7 +3483,7 @@
       <t xml:space="preserve">
 Later:
 15 Long Swordsmen
-5 Camlel Riders
+5 Camel Riders
 5 Light Cavalry
 5 Shrivamsha Riders
 10 Elephant Archers
@@ -2680,419 +3549,24 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-2 Light Cavalry
-2 Elite Elephant Archers
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-11 Chakram Throwers
-15 Elite Shrivamsha Riders
-12 Elite Elephant Archers
-5 Siege Elephants
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-8 Chakram Throwers
-12 Elite Shrivamsha Riders
-8 Elite Elephant Archers
-4 Siege Elephants
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-14 Chakram Throwers
-18 Elite Shrivamsha Riders
-12 Elite Elephant Archers
-6 Siege Elephants</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-1 Scout
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-13 Champions
-11 Halberdiers
-11 Elite Urumi Swordsmen
-8 Elite Elephant Archers
-3 Trebuchets
-5 Galleons (If the Player builds a Dock)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-10 Champions
-8 Halberdiers
-8 Elite Urumi Swordsmen
-5 Elite Elephant Archers
-2 Trebuchets
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-16 Champions
-14 Halberdiers
-14 Elite Urumi Swordsmen
-11 Elite Elephant Archers
-4 Trebuchets
-5 Galleons (If the Player builds a Dock)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-4 Long Swordsmen
-6 Arambai
-1 War Galley
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-11 Champions
-8 Elite Battle Elephants
-8 Elite Arambai
-4 Heavy Scorpions
-5 Capped Rams
-8 Galleons
-4 Fire Ships
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-8 Champions
-5 Elite Battle Elephants
-6 Elite Arambai
-3 Heavy Scorpions
-6 Galleons
-2 Fire Ships
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-13 Champions
-10 Elite Battle Elephants
-10 Elite Arambai
-5 Heavy Scorpions
-6 Capped Rams
-10 Galleons
-6 Fire Ships</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-84 Elite Ghulams
-21 Imperial Camel Riders
-29 Heavy Camel Riders
-1 Onager
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-75 Elite Ghulams
-75 Heavy Cavalry Archers
-75 Imperial Camel Riders
-4 Siege Elephants
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-50 Elite Ghulams
-50 Heavy Cavalry Archers
-50 Imperial Camel Riders
-2 Siege Elephants
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-100 Elite Ghulams
-100 Heavy Cavalry Archers
-100 Imperial Camel Riders
-6 Siege Elephants</t>
-    </r>
-  </si>
-  <si>
-    <t>6 Villagers, 1 Town Center, Misc. Units/Buildings (Indian Dynasties) x4
-Max Population Limit +25 x3</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Indian Dynasties</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ghorids</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Collect 1/2 Relic/s
-Destroy the </t>
-    </r>
+    <t>Elite Shrivamsha Rider</t>
+  </si>
+  <si>
+    <t>Elite Urumi Swordsman</t>
+  </si>
+  <si>
+    <t>Champion</t>
+  </si>
+  <si>
+    <t>Halberdier</t>
+  </si>
+  <si>
+    <t>Trade Cog</t>
+  </si>
+  <si>
+    <t>Galleon</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="14"/>
@@ -3100,92 +3574,68 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>Wonder</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Destroy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>1/2/3/4/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>5/6/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>7/8/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF2FE2F5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Castle/s
-</t>
-    </r>
-  </si>
-  <si>
-    <t>The Player needs to have unlocked Monasteries and Monks to collect Relics.</t>
-  </si>
-  <si>
-    <t>400 Food, 400 Wood, 300 Gold, 100 Stone x4
-Technology: 1 of Husbandry, Light Cavalry, Chain Barding Armor, Bow Saw
-Technology: 1 of Fervor, Sanctity, Long Swordsman, Arson, Chain Mail Armor, Heavy Plow
-Technology: 1 of Thumb Ring, Bodkin Arrow, Leather Archer Armor, Stone Shaft Mining
-Technology: 1 of Ballistics, Murder Holes, Guard Tower, Gold Shaft Mining
-Technology: Kshatriyas
-Technology: Frontier Guards
-Castles can be built</t>
-  </si>
-  <si>
-    <t>In Vanilla, the Player cannot build Castles in the Beginning.
-The Ghorids' Trade seems to be malfunctioning, it looks like the Trade Carts are repeatedly ordered back to the allied Market, so they never deliver their Gold.
-The Techs mentioned in the usefull items are given when a Raja has been converted, but only 1 of each Selection.</t>
-  </si>
-  <si>
-    <t>This Player recieves the Units Player 7 has created whenever a Raid happens.</t>
+      <t>Capped Ram</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Elite Arambai</t>
+  </si>
+  <si>
+    <t>Elite Battle Elephant</t>
+  </si>
+  <si>
+    <t>Elite Ghulam</t>
+  </si>
+  <si>
+    <t>Palisade Gate</t>
+  </si>
+  <si>
+    <t>Caravanserai</t>
+  </si>
+  <si>
+    <t>No Bombard Cannon
+No Hand Cannoneer
+No Cannon Galleon</t>
+  </si>
+  <si>
+    <t>Gold Mining
+Stone Mining
+Gold Shaft Mining
+Stone Shaft Mining
+Double-Bit Axe
+Bow Saw
+Bloodlines
+Husbandry
+Thumb Ring
+Arson
+Fishing Lines
+Gillnets
+Medium Warships
+Demolition Ship
+Dry Dock, Man-at-Arms, Long Swordsman, Light Cavalry, Elite Skirmisher and Crossbowman are researched automatically</t>
+  </si>
+  <si>
+    <t>Imperial Age is researched automatically on Standard</t>
+  </si>
+  <si>
+    <t>Husbandry, Light Cavalry, Chain Barding Armor, Bow Saw, Fervor, Sanctity, Long Swordsman, Arson, Chain Mail Armor, Heavy Plow, Thumb Ring, Bodkin Arrow, Leather Archer Armor, Stone Shaft Mining, Ballistics, Murder Holes, Guard Tower, Gold Shaft Mining, Kshatriyas and Frontier Guards researched when specific/enough Rajas are converted
+No Spies</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3286,6 +3736,18 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3295,7 +3757,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -3383,11 +3845,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3423,6 +3931,84 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3827,19 +4413,19 @@
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>31</v>
       </c>
       <c r="M4" s="7" t="s">
         <v>28</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
@@ -3852,35 +4438,35 @@
         <v>17</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
@@ -3890,41 +4476,41 @@
         <v>18</v>
       </c>
       <c r="C6" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>51</v>
-      </c>
       <c r="E6" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>43</v>
-      </c>
       <c r="I6" s="10" t="s">
-        <v>50</v>
+        <v>158</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>49</v>
+        <v>166</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
@@ -3934,36 +4520,36 @@
         <v>19</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>58</v>
-      </c>
       <c r="F7" s="9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>62</v>
+        <v>186</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>63</v>
+        <v>185</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
@@ -3974,49 +4560,49 @@
         <v>20</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="O8" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="K8" s="7" t="s">
+      <c r="P8" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q8" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q8" s="7" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="24" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4041,4 +4627,2609 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6341E6-F49D-4D9B-B8D5-49B8451F6CB4}">
+  <dimension ref="B1:L31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
+      <c r="G2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="33"/>
+      <c r="D3" s="34"/>
+      <c r="G3" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K3" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="16"/>
+      <c r="G6" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16"/>
+      <c r="G7" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="16"/>
+      <c r="G8" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16"/>
+      <c r="G9" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="16"/>
+      <c r="G10" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="16"/>
+      <c r="G11" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="16"/>
+      <c r="G12" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="G13" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K13" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="G14" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="G15" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="G16" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K23" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K24" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="H25" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="K25" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="K26" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8CC421-3ED5-419E-91AA-8028DB271924}">
+  <dimension ref="B1:L37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
+      <c r="G2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="33"/>
+      <c r="D3" s="34"/>
+      <c r="G3" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K3" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="16"/>
+      <c r="G6" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16"/>
+      <c r="G7" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="16"/>
+      <c r="G8" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16"/>
+      <c r="G9" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="16"/>
+      <c r="G10" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="16"/>
+      <c r="G11" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="16"/>
+      <c r="G12" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="16"/>
+      <c r="G13" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K13" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="16"/>
+      <c r="G14" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K14" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="16"/>
+      <c r="G15" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K15" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="16"/>
+      <c r="G16" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K16" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K17" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K18" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K19" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K27" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K28" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="K29" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K30" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{757DB1B6-91A3-4A83-999A-8323F5188665}">
+  <dimension ref="B1:L35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
+      <c r="G2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="33"/>
+      <c r="D3" s="34"/>
+      <c r="G3" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="16"/>
+      <c r="G6" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16"/>
+      <c r="G7" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="16"/>
+      <c r="G8" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16"/>
+      <c r="G9" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="16"/>
+      <c r="G10" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="16"/>
+      <c r="G11" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="16"/>
+      <c r="G12" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="16"/>
+      <c r="G13" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="K13" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="16"/>
+      <c r="G14" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="16"/>
+      <c r="G15" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="16"/>
+      <c r="G16" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K16" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K17" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G20" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="K20" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G21" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="K21" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G22" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G23" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G24" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="K25" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="K26" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="K27" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="K28" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="K29" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="30" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="K30" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="L30" s="21" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+    </row>
+    <row r="33" spans="11:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K33" s="27"/>
+      <c r="L33" s="27"/>
+    </row>
+    <row r="34" spans="11:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
+    </row>
+    <row r="35" spans="11:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K35" s="27"/>
+      <c r="L35" s="27"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE9E4D4-44CF-47C3-A8C8-A88C92B7478F}">
+  <dimension ref="B1:L37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
+      <c r="G2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="33"/>
+      <c r="D3" s="34"/>
+      <c r="G3" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="16"/>
+      <c r="G6" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16"/>
+      <c r="G7" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="16"/>
+      <c r="G8" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16"/>
+      <c r="G9" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="16"/>
+      <c r="G10" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="16"/>
+      <c r="G11" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="16"/>
+      <c r="G12" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="16"/>
+      <c r="G13" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="16"/>
+      <c r="G14" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="16"/>
+      <c r="G15" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="16"/>
+      <c r="G16" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G21" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K22" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K24" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="H33" s="21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+    </row>
+    <row r="35" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+    </row>
+    <row r="36" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+    </row>
+    <row r="37" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F13739A7-8F91-4E17-A27C-0AA597821225}">
+  <dimension ref="B1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
+      <c r="G2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="33"/>
+      <c r="D3" s="34"/>
+      <c r="G3" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="G5" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K5" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="16"/>
+      <c r="G6" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16"/>
+      <c r="G7" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="16"/>
+      <c r="G8" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K8" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16"/>
+      <c r="G9" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="16"/>
+      <c r="G10" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="16"/>
+      <c r="G11" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K11" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="16"/>
+      <c r="G12" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="16"/>
+      <c r="G13" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K13" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="16"/>
+      <c r="G14" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="16"/>
+      <c r="G15" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="16"/>
+      <c r="G16" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K16" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K17" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K22" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G23" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K23" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K24" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K25" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K26" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K27" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K28" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K29" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K30" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K31" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="L31" s="21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K32" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="L32" s="21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K33" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="L33" s="21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K34" s="23"/>
+      <c r="L34" s="23"/>
+    </row>
+    <row r="35" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G35" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K35" s="27"/>
+      <c r="L35" s="27"/>
+    </row>
+    <row r="36" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G36" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K36" s="27"/>
+      <c r="L36" s="27"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="H37" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="K37" s="27"/>
+      <c r="L37" s="27"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="K38" s="27"/>
+      <c r="L38" s="27"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="K39" s="27"/>
+      <c r="L39" s="27"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="K40" s="27"/>
+      <c r="L40" s="27"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="K41" s="27"/>
+      <c r="L41" s="27"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/Logic Requirements/Ageipelago Prithviraj.xlsx
+++ b/docs/Logic Requirements/Ageipelago Prithviraj.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4534A02-F6D5-438C-B085-77ED9ABE570A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4368DE-7ABB-4AA6-8B11-F006EDFE1DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Prithviraj" sheetId="1" r:id="rId1"/>
@@ -3567,26 +3567,6 @@
     <t>Galleon</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF2FE2F5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Capped Ram</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Not on Standard)</t>
-    </r>
-  </si>
-  <si>
     <t>Elite Arambai</t>
   </si>
   <si>
@@ -3630,12 +3610,33 @@
     <t>Husbandry, Light Cavalry, Chain Barding Armor, Bow Saw, Fervor, Sanctity, Long Swordsman, Arson, Chain Mail Armor, Heavy Plow, Thumb Ring, Bodkin Arrow, Leather Archer Armor, Stone Shaft Mining, Ballistics, Murder Holes, Guard Tower, Gold Shaft Mining, Kshatriyas and Frontier Guards researched when specific/enough Rajas are converted
 No Spies</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF2FE2F5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Capped Ram</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Not on Standard)</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3745,6 +3746,62 @@
     </font>
     <font>
       <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF2FE2F5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0" tint="-0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3895,7 +3952,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3981,6 +4038,18 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3999,16 +4068,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4644,11 +4731,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="31"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="35"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -4663,11 +4750,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="38"/>
       <c r="G3" s="9" t="s">
         <v>77</v>
       </c>
@@ -4897,7 +4984,7 @@
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="40" t="s">
         <v>124</v>
       </c>
       <c r="H16" s="9" t="s">
@@ -4925,7 +5012,7 @@
       </c>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="42" t="s">
         <v>126</v>
       </c>
       <c r="H18" s="9" t="s">
@@ -5101,11 +5188,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="31"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="35"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -5120,11 +5207,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="38"/>
       <c r="G3" s="9" t="s">
         <v>77</v>
       </c>
@@ -5211,7 +5298,7 @@
       <c r="H7" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K7" s="19" t="s">
+      <c r="K7" s="44" t="s">
         <v>153</v>
       </c>
       <c r="L7" s="9" t="s">
@@ -5456,7 +5543,7 @@
       </c>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="45" t="s">
         <v>127</v>
       </c>
       <c r="H23" s="9" t="s">
@@ -5498,13 +5585,13 @@
       </c>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="20" t="s">
+      <c r="G26" s="45" t="s">
         <v>150</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="K26" s="18" t="s">
+      <c r="K26" s="42" t="s">
         <v>155</v>
       </c>
       <c r="L26" s="9" t="s">
@@ -5512,13 +5599,13 @@
       </c>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="20" t="s">
+      <c r="G27" s="45" t="s">
         <v>151</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K27" s="18" t="s">
+      <c r="K27" s="42" t="s">
         <v>156</v>
       </c>
       <c r="L27" s="9" t="s">
@@ -5532,7 +5619,7 @@
       <c r="H28" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K28" s="18" t="s">
+      <c r="K28" s="42" t="s">
         <v>87</v>
       </c>
       <c r="L28" s="9" t="s">
@@ -5546,7 +5633,7 @@
       <c r="H29" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="K29" s="18" t="s">
+      <c r="K29" s="42" t="s">
         <v>89</v>
       </c>
       <c r="L29" s="9" t="s">
@@ -5554,7 +5641,7 @@
       </c>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="25" t="s">
+      <c r="G30" s="43" t="s">
         <v>152</v>
       </c>
       <c r="H30" s="9" t="s">
@@ -5650,11 +5737,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="31"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="35"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -5669,11 +5756,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="38"/>
       <c r="G3" s="9" t="s">
         <v>77</v>
       </c>
@@ -5718,7 +5805,7 @@
         <v>177</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>146</v>
@@ -5805,13 +5892,13 @@
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
       <c r="D10" s="16"/>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="40" t="s">
         <v>159</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="K10" s="44" t="s">
         <v>169</v>
       </c>
       <c r="L10" s="9" t="s">
@@ -5839,13 +5926,13 @@
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
       <c r="D12" s="16"/>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="40" t="s">
         <v>160</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K12" s="24" t="s">
+      <c r="K12" s="41" t="s">
         <v>170</v>
       </c>
       <c r="L12" s="9" t="s">
@@ -5896,7 +5983,7 @@
       <c r="H15" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="K15" s="18" t="s">
+      <c r="K15" s="42" t="s">
         <v>171</v>
       </c>
       <c r="L15" s="9" t="s">
@@ -5921,13 +6008,13 @@
       </c>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="44" t="s">
         <v>163</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K17" s="18" t="s">
+      <c r="K17" s="42" t="s">
         <v>172</v>
       </c>
       <c r="L17" s="9" t="s">
@@ -5991,7 +6078,7 @@
       </c>
     </row>
     <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="42" t="s">
         <v>175</v>
       </c>
       <c r="H22" s="9" t="s">
@@ -6005,7 +6092,7 @@
       </c>
     </row>
     <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="42" t="s">
         <v>167</v>
       </c>
       <c r="H23" s="9" t="s">
@@ -6139,11 +6226,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="31"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="35"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -6158,11 +6245,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="38"/>
       <c r="G3" s="9" t="s">
         <v>143</v>
       </c>
@@ -6204,10 +6291,10 @@
         <v>84</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>117</v>
@@ -6307,11 +6394,11 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
       <c r="D11" s="16"/>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="39" t="s">
         <v>178</v>
       </c>
       <c r="H11" s="9" t="s">
@@ -6379,7 +6466,7 @@
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
       <c r="D15" s="16"/>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="40" t="s">
         <v>179</v>
       </c>
       <c r="H15" s="9" t="s">
@@ -6452,7 +6539,7 @@
       </c>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="40" t="s">
         <v>181</v>
       </c>
       <c r="H20" s="9" t="s">
@@ -6480,7 +6567,7 @@
       </c>
     </row>
     <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="42" t="s">
         <v>183</v>
       </c>
       <c r="H22" s="9" t="s">
@@ -6494,7 +6581,7 @@
       </c>
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="42" t="s">
         <v>184</v>
       </c>
       <c r="H23" s="9" t="s">
@@ -6508,13 +6595,13 @@
       </c>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="18" t="s">
+      <c r="G24" s="42" t="s">
         <v>187</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K24" s="35" t="s">
+      <c r="K24" s="29" t="s">
         <v>157</v>
       </c>
       <c r="L24" s="21" t="s">
@@ -6522,7 +6609,7 @@
       </c>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="18" t="s">
+      <c r="G25" s="42" t="s">
         <v>188</v>
       </c>
       <c r="H25" s="9" t="s">
@@ -6532,7 +6619,7 @@
       <c r="L25" s="23"/>
     </row>
     <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="18" t="s">
+      <c r="G26" s="42" t="s">
         <v>189</v>
       </c>
       <c r="H26" s="9" t="s">
@@ -6562,7 +6649,7 @@
       <c r="L28" s="27"/>
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="24" t="s">
+      <c r="G29" s="41" t="s">
         <v>190</v>
       </c>
       <c r="H29" s="9" t="s">
@@ -6572,7 +6659,7 @@
       <c r="L29" s="27"/>
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="24" t="s">
+      <c r="G30" s="41" t="s">
         <v>191</v>
       </c>
       <c r="H30" s="9" t="s">
@@ -6600,7 +6687,7 @@
       </c>
     </row>
     <row r="33" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="35" t="s">
+      <c r="G33" s="46" t="s">
         <v>194</v>
       </c>
       <c r="H33" s="21" t="s">
@@ -6648,11 +6735,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="31"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="35"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -6667,12 +6754,12 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
-      <c r="G3" s="36" t="s">
+      <c r="C3" s="37"/>
+      <c r="D3" s="38"/>
+      <c r="G3" s="30" t="s">
         <v>77</v>
       </c>
       <c r="H3" s="9" t="s">
@@ -6695,8 +6782,8 @@
       <c r="D4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G4" s="36" t="s">
-        <v>113</v>
+      <c r="G4" s="30" t="s">
+        <v>117</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>78</v>
@@ -6713,19 +6800,19 @@
         <v>84</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="G5" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="G5" s="30" t="s">
         <v>144</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K5" s="18" t="s">
-        <v>208</v>
+      <c r="K5" s="42" t="s">
+        <v>207</v>
       </c>
       <c r="L5" s="9" t="s">
         <v>78</v>
@@ -6735,7 +6822,7 @@
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
       <c r="D6" s="16"/>
-      <c r="G6" s="36" t="s">
+      <c r="G6" s="30" t="s">
         <v>118</v>
       </c>
       <c r="H6" s="9" t="s">
@@ -6752,7 +6839,7 @@
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="16"/>
-      <c r="G7" s="36" t="s">
+      <c r="G7" s="30" t="s">
         <v>146</v>
       </c>
       <c r="H7" s="9" t="s">
@@ -6769,7 +6856,7 @@
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="16"/>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="42" t="s">
         <v>196</v>
       </c>
       <c r="H8" s="9" t="s">
@@ -6820,7 +6907,7 @@
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
       <c r="D11" s="16"/>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="42" t="s">
         <v>198</v>
       </c>
       <c r="H11" s="9" t="s">
@@ -6888,7 +6975,7 @@
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
       <c r="D15" s="16"/>
-      <c r="G15" s="24" t="s">
+      <c r="G15" s="41" t="s">
         <v>199</v>
       </c>
       <c r="H15" s="9" t="s">
@@ -6905,7 +6992,7 @@
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
       <c r="D16" s="16"/>
-      <c r="G16" s="24" t="s">
+      <c r="G16" s="41" t="s">
         <v>200</v>
       </c>
       <c r="H16" s="9" t="s">
@@ -6919,7 +7006,7 @@
       </c>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="24" t="s">
+      <c r="G17" s="41" t="s">
         <v>201</v>
       </c>
       <c r="H17" s="9" t="s">
@@ -6947,7 +7034,7 @@
       </c>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="24" t="s">
+      <c r="G19" s="41" t="s">
         <v>202</v>
       </c>
       <c r="H19" s="9" t="s">
@@ -6975,7 +7062,7 @@
       </c>
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="25" t="s">
+      <c r="G21" s="43" t="s">
         <v>203</v>
       </c>
       <c r="H21" s="9" t="s">
@@ -7004,7 +7091,7 @@
     </row>
     <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G23" s="9" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="H23" s="9" t="s">
         <v>78</v>
@@ -7017,8 +7104,8 @@
       </c>
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="25" t="s">
-        <v>205</v>
+      <c r="G24" s="43" t="s">
+        <v>204</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>78</v>
@@ -7044,9 +7131,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="25" t="s">
-        <v>206</v>
+    <row r="26" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G26" s="43" t="s">
+        <v>205</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>78</v>
@@ -7121,7 +7208,7 @@
       <c r="H31" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K31" s="37" t="s">
+      <c r="K31" s="31" t="s">
         <v>138</v>
       </c>
       <c r="L31" s="21" t="s">
@@ -7135,7 +7222,7 @@
       <c r="H32" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K32" s="37" t="s">
+      <c r="K32" s="31" t="s">
         <v>139</v>
       </c>
       <c r="L32" s="21" t="s">
@@ -7143,22 +7230,22 @@
       </c>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="37" t="s">
+      <c r="G33" s="31" t="s">
         <v>101</v>
       </c>
       <c r="H33" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K33" s="38" t="s">
-        <v>209</v>
+      <c r="K33" s="48" t="s">
+        <v>208</v>
       </c>
       <c r="L33" s="21" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="37" t="s">
-        <v>207</v>
+      <c r="G34" s="47" t="s">
+        <v>206</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>78</v>
@@ -7167,7 +7254,7 @@
       <c r="L34" s="23"/>
     </row>
     <row r="35" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G35" s="37" t="s">
+      <c r="G35" s="31" t="s">
         <v>161</v>
       </c>
       <c r="H35" s="9" t="s">
@@ -7177,7 +7264,7 @@
       <c r="L35" s="27"/>
     </row>
     <row r="36" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G36" s="37" t="s">
+      <c r="G36" s="31" t="s">
         <v>182</v>
       </c>
       <c r="H36" s="9" t="s">
@@ -7187,7 +7274,7 @@
       <c r="L36" s="27"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="38" t="s">
+      <c r="G37" s="32" t="s">
         <v>123</v>
       </c>
       <c r="H37" s="21" t="s">
